--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_98_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_98_R10.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6025</v>
+        <v>4.5757</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5239</v>
+        <v>4.3627</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0786</v>
+        <v>0.213</v>
       </c>
       <c r="G2" t="n">
         <v>5.9613</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2469</v>
+        <v>0.2201</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7591</v>
+        <v>0.5979</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5122</v>
+        <v>-0.3778</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6778999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6207</v>
+        <v>2.6748</v>
       </c>
       <c r="E3" t="n">
-        <v>1.836</v>
+        <v>1.3523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7847</v>
+        <v>1.3224</v>
       </c>
       <c r="G3" t="n">
         <v>4.0681</v>
@@ -688,13 +688,13 @@
         <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1406</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2467</v>
+        <v>0.7631</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3873</v>
+        <v>-0.8496</v>
       </c>
       <c r="V3" t="n">
         <v>-2.0026</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3531</v>
+        <v>2.604</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6544</v>
+        <v>2.0396</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6988</v>
+        <v>0.5643</v>
       </c>
       <c r="G4" t="n">
         <v>0.4323</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4709</v>
+        <v>-0.2201</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2003</v>
+        <v>0.1849</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2706</v>
+        <v>-0.405</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2716</v>
+        <v>1.3716</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5934</v>
+        <v>-1.0902</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8651</v>
+        <v>2.4618</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5872000000000001</v>
@@ -844,13 +844,13 @@
         <v>2.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1476</v>
+        <v>0.2475</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1019</v>
+        <v>0.4013</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2495</v>
+        <v>-0.1537</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2041</v>
+        <v>0.4157</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0392</v>
+        <v>0.7484</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.165</v>
+        <v>-0.3327</v>
       </c>
       <c r="G6" t="n">
-        <v>1.364</v>
+        <v>0.8984</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1249</v>
+        <v>2.0226</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4889</v>
+        <v>-1.1242</v>
       </c>
       <c r="J6" t="n">
-        <v>1.893</v>
+        <v>0.9588</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2283</v>
+        <v>1.1329</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1212</v>
+        <v>-0.1741</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.529</v>
+        <v>-0.0604</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1034</v>
+        <v>0.8897</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6323</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9419</v>
+        <v>-0.4079</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4323</v>
+        <v>0.2715</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.6794</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3943</v>
+        <v>-1.4665</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8197</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3735</v>
+        <v>0.2483</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1273</v>
+        <v>0.3461</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5008</v>
+        <v>-0.0978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8984</v>
+        <v>1.364</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0226</v>
+        <v>-0.1249</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1242</v>
+        <v>1.4889</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9588</v>
+        <v>1.893</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1329</v>
+        <v>-0.2283</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1741</v>
+        <v>2.1212</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0604</v>
+        <v>-0.529</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8897</v>
+        <v>0.1034</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.6323</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1971</v>
+        <v>-0.4894</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3497</v>
+        <v>-0.047</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8474</v>
+        <v>-0.4424</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4665</v>
+        <v>-0.3943</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.8197</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>N. SESTINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5231</v>
+        <v>-0.3122</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2025</v>
+        <v>-0.1886</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6794</v>
+        <v>-0.1236</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7829</v>
+        <v>-1.1879</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0841</v>
+        <v>0.1706</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3012</v>
+        <v>-1.3585</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8506</v>
+        <v>-0.2909</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9978</v>
+        <v>0.0672</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1472</v>
+        <v>-0.3581</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0678</v>
+        <v>-0.897</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0862</v>
+        <v>0.1034</v>
       </c>
       <c r="O8" t="n">
-        <v>0.154</v>
+        <v>-1.0004</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6515</v>
+        <v>-0.284</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8259</v>
+        <v>0.1024</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1744</v>
+        <v>-0.3864</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. SESTINA</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7236</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4991</v>
+        <v>-2.5996</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2245</v>
+        <v>1.713</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1879</v>
+        <v>-0.7829</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1706</v>
+        <v>-1.0841</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3585</v>
+        <v>0.3012</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2909</v>
+        <v>-0.8506</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0672</v>
+        <v>-0.9978</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3581</v>
+        <v>0.1472</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.897</v>
+        <v>0.0678</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1034</v>
+        <v>-0.0862</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0004</v>
+        <v>0.154</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6954</v>
+        <v>0.288</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2082</v>
+        <v>0.4288</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4872</v>
+        <v>-0.1408</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0768</v>
+        <v>-1.6242</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0693</v>
+        <v>-3.1126</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9925</v>
+        <v>1.4884</v>
       </c>
       <c r="G10" t="n">
         <v>1.0747</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2401</v>
+        <v>0.6928</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8417</v>
+        <v>0.7984</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3985</v>
+        <v>-0.1056</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.946799999999998</v>
+        <v>9.0671</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7381000000000002</v>
+        <v>1.858099999999999</v>
       </c>
       <c r="F11" t="n">
         <v>7.2088</v>
@@ -1312,10 +1312,10 @@
         <v>19.716</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1598</v>
+        <v>-0.03949999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>2.381</v>
+        <v>3.5013</v>
       </c>
       <c r="U11" t="n">
         <v>-3.5407</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8961</v>
+        <v>6.2006</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6471</v>
+        <v>5.883</v>
       </c>
       <c r="F12" t="n">
-        <v>0.249</v>
+        <v>0.3175</v>
       </c>
       <c r="G12" t="n">
         <v>4.058</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3717</v>
+        <v>0.6761</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0395</v>
+        <v>0.2754</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3321</v>
+        <v>0.4007</v>
       </c>
       <c r="V12" t="n">
         <v>1.4665</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9167</v>
+        <v>1.405</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0939</v>
+        <v>2.9759</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1772</v>
+        <v>-1.5709</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5339</v>
@@ -1468,13 +1468,13 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3743</v>
+        <v>0.114</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5272</v>
+        <v>0.4092</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9014</v>
+        <v>-0.2952</v>
       </c>
       <c r="V13" t="n">
         <v>3.2166</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2039</v>
+        <v>-0.1557</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4906</v>
+        <v>0.7829</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2867</v>
+        <v>-0.9386</v>
       </c>
       <c r="G14" t="n">
         <v>0.0881</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>0.51</v>
+        <v>0.1505</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1641</v>
+        <v>0.4564</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6541</v>
+        <v>-0.306</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3943</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.551</v>
+        <v>-1.0063</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2262</v>
+        <v>-1.816</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6752</v>
+        <v>0.8097</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0665</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>1.281</v>
+        <v>0.8257</v>
       </c>
       <c r="T15" t="n">
-        <v>1.274</v>
+        <v>0.6842</v>
       </c>
       <c r="U15" t="n">
-        <v>0.007</v>
+        <v>0.1415</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.9717</v>
+        <v>-1.8546</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8874</v>
+        <v>-3.6829</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0842</v>
+        <v>1.8282</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.3348</v>
+        <v>-4.2664</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.755</v>
+        <v>-2.1884</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.5799</v>
+        <v>-2.0779</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1371</v>
+        <v>-4.5772</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4012</v>
+        <v>-2.2918</v>
       </c>
       <c r="L16" t="n">
-        <v>0.264</v>
+        <v>-2.2854</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1977</v>
+        <v>0.3109</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6462</v>
+        <v>0.1034</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.8439</v>
+        <v>0.2075</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3631</v>
+        <v>0.2673</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8011</v>
+        <v>0.1417</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.438</v>
+        <v>0.1256</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.6822</v>
+        <v>-2.174</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.5583</v>
+        <v>-2.5952</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8761</v>
+        <v>0.4212</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.1747</v>
+        <v>-3.3348</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2207</v>
+        <v>-0.755</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9539</v>
+        <v>-2.5799</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.967</v>
+        <v>-1.1371</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.2246</v>
+        <v>-1.4012</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2576</v>
+        <v>0.264</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2077</v>
+        <v>-2.1977</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0039</v>
+        <v>0.6462</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2116</v>
+        <v>-2.8439</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1883</v>
+        <v>1.1608</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6765</v>
+        <v>1.0934</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5118</v>
+        <v>0.0674</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8705</v>
+        <v>-2.3835</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.2726</v>
+        <v>-3.2045</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4021</v>
+        <v>0.821</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.2664</v>
+        <v>-3.1747</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1884</v>
+        <v>-1.2207</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0779</v>
+        <v>-1.9539</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.5772</v>
+        <v>-1.967</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.2918</v>
+        <v>-2.2246</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.2854</v>
+        <v>0.2576</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3109</v>
+        <v>-1.2077</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1034</v>
+        <v>1.0039</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2075</v>
+        <v>-2.2116</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7486</v>
+        <v>1.487</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4481</v>
+        <v>1.0304</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3005</v>
+        <v>0.4567</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1444</v>
+        <v>0.2836</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4386</v>
+        <v>-2.5566</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.83</v>
+        <v>-2.84</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6086</v>
+        <v>0.2834</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6657</v>
+        <v>-3.3449</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4382</v>
+        <v>-0.4607</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2275</v>
+        <v>-2.8842</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2118</v>
+        <v>-1.311</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2486</v>
+        <v>0.1512</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-1.4623</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4539</v>
+        <v>-2.0339</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1896</v>
+        <v>-0.612</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2643</v>
+        <v>-1.422</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>2.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7033</v>
+        <v>-0.8353</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2987</v>
+        <v>-0.3692</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4046</v>
+        <v>-0.4661</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4495</v>
+        <v>-3.0625</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6657</v>
+        <v>-2.7121</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2162</v>
+        <v>-0.3505</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3449</v>
+        <v>-0.6657</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4607</v>
+        <v>-0.4382</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.8842</v>
+        <v>-0.2275</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.311</v>
+        <v>-0.2118</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1512</v>
+        <v>-0.2486</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4623</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0339</v>
+        <v>-0.4539</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.612</v>
+        <v>-0.1896</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.422</v>
+        <v>-0.2643</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7282</v>
+        <v>-0.3273</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1949</v>
+        <v>-0.1808</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5333</v>
+        <v>-0.1465</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,28 +2047,28 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.946800000000001</v>
+        <v>-5.5876</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.208600000000001</v>
+        <v>-7.2089</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7381</v>
+        <v>1.621</v>
       </c>
       <c r="G21" t="n">
         <v>-11.2408</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5747</v>
+        <v>-2.574700000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-8.666</v>
+        <v>-8.665999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.03659999999999997</v>
+        <v>-0.03659999999999974</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.017399999999999</v>
+        <v>-4.0174</v>
       </c>
       <c r="L21" t="n">
         <v>3.980700000000001</v>
@@ -2083,7 +2083,7 @@
         <v>-12.6469</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.4793</v>
+        <v>-3.479299999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-19.7159</v>
@@ -2092,13 +2092,13 @@
         <v>16.2366</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1597</v>
+        <v>3.5188</v>
       </c>
       <c r="T21" t="n">
         <v>3.5407</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.381</v>
+        <v>-0.02190000000000003</v>
       </c>
       <c r="V21" t="n">
         <v>5.613499999999999</v>
